--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>96253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460585.3979818156</v>
+        <v>460585</v>
       </c>
       <c r="R2" t="n">
-        <v>6495331.702450257</v>
+        <v>6495332</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -744,19 +739,9 @@
           <t>1982-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1982-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460585.3979818156</v>
+        <v>460585</v>
       </c>
       <c r="R3" t="n">
-        <v>6495331.702450257</v>
+        <v>6495332</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -860,19 +840,9 @@
           <t>1982-07-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1982-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98608</v>
+        <v>98616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5943608</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>2900959</v>
       </c>
       <c r="B3" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7823-2022 artfynd.xlsx
+++ b/artfynd/A 7823-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5943608</v>
+        <v>2900959</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2900959</v>
+        <v>5943608</v>
       </c>
       <c r="B3" t="n">
-        <v>98683</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,23 +787,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
